--- a/ltt/ValueSet-fkgateway-ltt-care-plan-activity-types.xlsx
+++ b/ltt/ValueSet-fkgateway-ltt-care-plan-activity-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-31T13:04:54+02:00</t>
+    <t>2025-10-29T22:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
